--- a/inquiry_forms/034_high_speed_server_inquiry_form--inquiry_forms.xlsx
+++ b/inquiry_forms/034_high_speed_server_inquiry_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'dedicated',_'label':_'dedicated'}</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'dedicated', 'label': 'Dedicated'}</t>
+          <t>Dedicated</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'virtual',_'label':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'virtual', 'label': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'managed',_'label':_'managed'}</t>
+          <t>managed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'managed', 'label': 'Managed'}</t>
+          <t>Managed</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'annually',_'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'annually', 'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'one_time',_'label':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'one_time', 'label': 'One-time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'not_started',_'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'not_started', 'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress',_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'in_progress', 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'declined',_'label':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'declined', 'label': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
